--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CLUB ESPORTIU BÀSQUET LLÍRIA.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CLUB ESPORTIU BÀSQUET LLÍRIA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>A. MEANA PEREZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>53.1248</v>
+        <v>57.5204</v>
       </c>
       <c r="E2" t="n">
-        <v>35.2198</v>
+        <v>59.9768</v>
       </c>
       <c r="F2" t="n">
-        <v>17.9051</v>
+        <v>-2.455999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>12.7302</v>
+        <v>55.6725</v>
       </c>
       <c r="H2" t="n">
-        <v>5.0585</v>
+        <v>-22.8029</v>
       </c>
       <c r="I2" t="n">
-        <v>7.6717</v>
+        <v>78.47490000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>23.3041</v>
+        <v>77.31949999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>16.2003</v>
+        <v>-1.0087</v>
       </c>
       <c r="L2" t="n">
-        <v>7.1039</v>
+        <v>78.3279</v>
       </c>
       <c r="M2" t="n">
-        <v>-10.5744</v>
+        <v>-21.6471</v>
       </c>
       <c r="N2" t="n">
-        <v>-11.142</v>
+        <v>-21.7941</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5678000000000004</v>
+        <v>0.1469</v>
       </c>
       <c r="P2" t="n">
-        <v>-10.8829</v>
+        <v>-30.1853</v>
       </c>
       <c r="Q2" t="n">
-        <v>-42.5057</v>
+        <v>-71.0484</v>
       </c>
       <c r="R2" t="n">
-        <v>31.6228</v>
+        <v>40.8631</v>
       </c>
       <c r="S2" t="n">
-        <v>50.6392</v>
+        <v>-1.0645</v>
       </c>
       <c r="T2" t="n">
-        <v>37.8941</v>
+        <v>-0.3842</v>
       </c>
       <c r="U2" t="n">
-        <v>12.7449</v>
+        <v>-0.6798999999999996</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6387999999999999</v>
+        <v>33.0977</v>
       </c>
       <c r="W2" t="n">
-        <v>16.527</v>
+        <v>54.0894</v>
       </c>
       <c r="X2" t="n">
-        <v>-15.8882</v>
+        <v>-20.9916</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MEANA PEREZ</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>40.2717</v>
+        <v>23.7689</v>
       </c>
       <c r="E3" t="n">
-        <v>48.745</v>
+        <v>12.4013</v>
       </c>
       <c r="F3" t="n">
-        <v>-8.473100000000001</v>
+        <v>11.3679</v>
       </c>
       <c r="G3" t="n">
-        <v>55.6725</v>
+        <v>12.7302</v>
       </c>
       <c r="H3" t="n">
-        <v>-22.8029</v>
+        <v>5.0585</v>
       </c>
       <c r="I3" t="n">
-        <v>78.47490000000001</v>
+        <v>7.6717</v>
       </c>
       <c r="J3" t="n">
-        <v>77.31949999999999</v>
+        <v>23.3041</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.0087</v>
+        <v>16.2003</v>
       </c>
       <c r="L3" t="n">
-        <v>78.3279</v>
+        <v>7.1039</v>
       </c>
       <c r="M3" t="n">
-        <v>-21.6471</v>
+        <v>-10.5744</v>
       </c>
       <c r="N3" t="n">
-        <v>-21.7941</v>
+        <v>-11.142</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1469</v>
+        <v>0.5678000000000004</v>
       </c>
       <c r="P3" t="n">
-        <v>-30.1853</v>
+        <v>-10.8829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-71.0484</v>
+        <v>-42.5057</v>
       </c>
       <c r="R3" t="n">
-        <v>40.8631</v>
+        <v>31.6228</v>
       </c>
       <c r="S3" t="n">
-        <v>-18.313</v>
+        <v>21.283</v>
       </c>
       <c r="T3" t="n">
-        <v>-11.6159</v>
+        <v>15.0757</v>
       </c>
       <c r="U3" t="n">
-        <v>-6.6973</v>
+        <v>6.2075</v>
       </c>
       <c r="V3" t="n">
-        <v>33.0977</v>
+        <v>0.6387999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>54.0894</v>
+        <v>16.527</v>
       </c>
       <c r="X3" t="n">
-        <v>-20.9916</v>
+        <v>-15.8882</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>28.986</v>
+        <v>12.4962</v>
       </c>
       <c r="E4" t="n">
-        <v>25.8013</v>
+        <v>9.3361</v>
       </c>
       <c r="F4" t="n">
-        <v>3.185099999999999</v>
+        <v>3.1605</v>
       </c>
       <c r="G4" t="n">
         <v>15.8089</v>
@@ -766,13 +766,13 @@
         <v>37.9883</v>
       </c>
       <c r="S4" t="n">
-        <v>26.6892</v>
+        <v>10.1995</v>
       </c>
       <c r="T4" t="n">
-        <v>22.6248</v>
+        <v>6.1599</v>
       </c>
       <c r="U4" t="n">
-        <v>4.0642</v>
+        <v>4.0393</v>
       </c>
       <c r="V4" t="n">
         <v>-16.1815</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. BONO SOLER</t>
+          <t>V. PEREZ TOMAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>13.2058</v>
+        <v>12.1368</v>
       </c>
       <c r="E5" t="n">
-        <v>3.655</v>
+        <v>11.4667</v>
       </c>
       <c r="F5" t="n">
-        <v>9.551299999999999</v>
+        <v>0.6700999999999993</v>
       </c>
       <c r="G5" t="n">
-        <v>3.972</v>
+        <v>25.3243</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.9988</v>
+        <v>-0.1571000000000008</v>
       </c>
       <c r="I5" t="n">
-        <v>8.9711</v>
+        <v>25.4819</v>
       </c>
       <c r="J5" t="n">
-        <v>9.9777</v>
+        <v>42.8257</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9543</v>
+        <v>13.4457</v>
       </c>
       <c r="L5" t="n">
-        <v>7.023700000000001</v>
+        <v>29.38</v>
       </c>
       <c r="M5" t="n">
-        <v>-6.005800000000001</v>
+        <v>-17.5017</v>
       </c>
       <c r="N5" t="n">
-        <v>-7.9531</v>
+        <v>-13.6034</v>
       </c>
       <c r="O5" t="n">
-        <v>1.9471</v>
+        <v>-3.8987</v>
       </c>
       <c r="P5" t="n">
-        <v>8.2135</v>
+        <v>-14.5793</v>
       </c>
       <c r="Q5" t="n">
-        <v>-10.8831</v>
+        <v>-40.6575</v>
       </c>
       <c r="R5" t="n">
-        <v>19.0967</v>
+        <v>26.0784</v>
       </c>
       <c r="S5" t="n">
-        <v>6.7576</v>
+        <v>-1.729</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4819</v>
+        <v>-1.2227</v>
       </c>
       <c r="U5" t="n">
-        <v>5.2752</v>
+        <v>-0.5061</v>
       </c>
       <c r="V5" t="n">
-        <v>-5.7369</v>
+        <v>3.1207</v>
       </c>
       <c r="W5" t="n">
-        <v>3.0779</v>
+        <v>10.5214</v>
       </c>
       <c r="X5" t="n">
-        <v>-8.8147</v>
+        <v>-7.4005</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. GALLEGO MOGRO</t>
+          <t>P. BONO SOLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>10.2168</v>
+        <v>11.1539</v>
       </c>
       <c r="E6" t="n">
-        <v>10.1246</v>
+        <v>3.2017</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09219999999999995</v>
+        <v>7.9521</v>
       </c>
       <c r="G6" t="n">
-        <v>-12.0171</v>
+        <v>3.972</v>
       </c>
       <c r="H6" t="n">
-        <v>-9.100899999999999</v>
+        <v>-4.9988</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.9161</v>
+        <v>8.9711</v>
       </c>
       <c r="J6" t="n">
-        <v>10.8726</v>
+        <v>9.9777</v>
       </c>
       <c r="K6" t="n">
-        <v>8.7064</v>
+        <v>2.9543</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1662</v>
+        <v>7.023700000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-22.8898</v>
+        <v>-6.005800000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-17.8075</v>
+        <v>-7.9531</v>
       </c>
       <c r="O6" t="n">
-        <v>-5.0824</v>
+        <v>1.9471</v>
       </c>
       <c r="P6" t="n">
-        <v>13.5527</v>
+        <v>8.2135</v>
       </c>
       <c r="Q6" t="n">
-        <v>-15.4005</v>
+        <v>-10.8831</v>
       </c>
       <c r="R6" t="n">
-        <v>28.9531</v>
+        <v>19.0967</v>
       </c>
       <c r="S6" t="n">
-        <v>11.0568</v>
+        <v>4.7049</v>
       </c>
       <c r="T6" t="n">
-        <v>9.3264</v>
+        <v>1.0289</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7306</v>
+        <v>3.6759</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.3751</v>
+        <v>-5.7369</v>
       </c>
       <c r="W6" t="n">
-        <v>5.3263</v>
+        <v>3.0779</v>
       </c>
       <c r="X6" t="n">
-        <v>-7.7014</v>
+        <v>-8.8147</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. PEREZ TOMAS</t>
+          <t>S. GALLEGO MOGRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.01340000000000074</v>
+        <v>8.159800000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>2.121900000000001</v>
+        <v>7.962899999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1355</v>
+        <v>0.1969999999999998</v>
       </c>
       <c r="G7" t="n">
-        <v>25.3243</v>
+        <v>-12.0171</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1571000000000008</v>
+        <v>-9.100899999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>25.4819</v>
+        <v>-2.9161</v>
       </c>
       <c r="J7" t="n">
-        <v>42.8257</v>
+        <v>10.8726</v>
       </c>
       <c r="K7" t="n">
-        <v>13.4457</v>
+        <v>8.7064</v>
       </c>
       <c r="L7" t="n">
-        <v>29.38</v>
+        <v>2.1662</v>
       </c>
       <c r="M7" t="n">
-        <v>-17.5017</v>
+        <v>-22.8898</v>
       </c>
       <c r="N7" t="n">
-        <v>-13.6034</v>
+        <v>-17.8075</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.8987</v>
+        <v>-5.0824</v>
       </c>
       <c r="P7" t="n">
-        <v>-14.5793</v>
+        <v>13.5527</v>
       </c>
       <c r="Q7" t="n">
-        <v>-40.6575</v>
+        <v>-15.4005</v>
       </c>
       <c r="R7" t="n">
-        <v>26.0784</v>
+        <v>28.9531</v>
       </c>
       <c r="S7" t="n">
-        <v>-13.879</v>
+        <v>8.9999</v>
       </c>
       <c r="T7" t="n">
-        <v>-10.5675</v>
+        <v>7.1648</v>
       </c>
       <c r="U7" t="n">
-        <v>-3.3114</v>
+        <v>1.835</v>
       </c>
       <c r="V7" t="n">
-        <v>3.1207</v>
+        <v>-2.3751</v>
       </c>
       <c r="W7" t="n">
-        <v>10.5214</v>
+        <v>5.3263</v>
       </c>
       <c r="X7" t="n">
-        <v>-7.4005</v>
+        <v>-7.7014</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. NAVARRO MALDONADO</t>
+          <t>D. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.604</v>
+        <v>5.188400000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5895</v>
+        <v>-13.7774</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0146</v>
+        <v>18.9661</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0686</v>
+        <v>2.658500000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2338</v>
+        <v>-14.2185</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3024</v>
+        <v>16.8765</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4915999999999999</v>
+        <v>16.0237</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6</v>
+        <v>0.6291</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0916</v>
+        <v>15.3949</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5769000000000002</v>
+        <v>-13.3656</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3661</v>
+        <v>-14.8477</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2108000000000002</v>
+        <v>1.482000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6428</v>
+        <v>3.4909</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0534</v>
+        <v>-35.1136</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4106</v>
+        <v>38.6042</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3234</v>
+        <v>-0.8724000000000003</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3293</v>
+        <v>0.5073000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9939999999999999</v>
+        <v>-1.3801</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.7063</v>
+        <v>-0.08789999999999987</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6982</v>
+        <v>4.804600000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.0081</v>
+        <v>-4.892200000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. RIVAS PALMER</t>
+          <t>E. HERRERA SAURET</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.593900000000001</v>
+        <v>2.866300000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-20.937</v>
+        <v>5.9837</v>
       </c>
       <c r="F9" t="n">
-        <v>13.3432</v>
+        <v>-3.1174</v>
       </c>
       <c r="G9" t="n">
-        <v>2.658500000000001</v>
+        <v>3.107400000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-14.2185</v>
+        <v>-13.5827</v>
       </c>
       <c r="I9" t="n">
-        <v>16.8765</v>
+        <v>16.6902</v>
       </c>
       <c r="J9" t="n">
-        <v>16.0237</v>
+        <v>18.5517</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6291</v>
+        <v>2.2479</v>
       </c>
       <c r="L9" t="n">
-        <v>15.3949</v>
+        <v>16.3036</v>
       </c>
       <c r="M9" t="n">
-        <v>-13.3656</v>
+        <v>-15.4441</v>
       </c>
       <c r="N9" t="n">
-        <v>-14.8477</v>
+        <v>-15.8308</v>
       </c>
       <c r="O9" t="n">
-        <v>1.482000000000001</v>
+        <v>0.3868000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>3.4909</v>
+        <v>-3.0801</v>
       </c>
       <c r="Q9" t="n">
-        <v>-35.1136</v>
+        <v>-34.908</v>
       </c>
       <c r="R9" t="n">
-        <v>38.6042</v>
+        <v>31.8285</v>
       </c>
       <c r="S9" t="n">
-        <v>-13.655</v>
+        <v>7.9295</v>
       </c>
       <c r="T9" t="n">
-        <v>-6.652</v>
+        <v>2.6078</v>
       </c>
       <c r="U9" t="n">
-        <v>-7.002899999999999</v>
+        <v>5.322</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.08789999999999987</v>
+        <v>-5.0905</v>
       </c>
       <c r="W9" t="n">
-        <v>4.804600000000001</v>
+        <v>19.7323</v>
       </c>
       <c r="X9" t="n">
-        <v>-4.892200000000001</v>
+        <v>-24.8233</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. HERRERA SAURET</t>
+          <t>P. NAVARRO MALDONADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.987300000000001</v>
+        <v>-4.1753</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.387900000000001</v>
+        <v>-2.419</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.599299999999999</v>
+        <v>-1.7564</v>
       </c>
       <c r="G10" t="n">
-        <v>3.107400000000001</v>
+        <v>1.0686</v>
       </c>
       <c r="H10" t="n">
-        <v>-13.5827</v>
+        <v>-0.2338</v>
       </c>
       <c r="I10" t="n">
-        <v>16.6902</v>
+        <v>1.3024</v>
       </c>
       <c r="J10" t="n">
-        <v>18.5517</v>
+        <v>0.4915999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2479</v>
+        <v>-0.6</v>
       </c>
       <c r="L10" t="n">
-        <v>16.3036</v>
+        <v>1.0916</v>
       </c>
       <c r="M10" t="n">
-        <v>-15.4441</v>
+        <v>0.5769000000000002</v>
       </c>
       <c r="N10" t="n">
-        <v>-15.8308</v>
+        <v>0.3661</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3868000000000001</v>
+        <v>0.2108000000000002</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.0801</v>
+        <v>-1.6428</v>
       </c>
       <c r="Q10" t="n">
-        <v>-34.908</v>
+        <v>-2.0534</v>
       </c>
       <c r="R10" t="n">
-        <v>31.8285</v>
+        <v>0.4106</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.9238</v>
+        <v>-0.8949</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.7641</v>
+        <v>-0.1589</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8402</v>
+        <v>-0.736</v>
       </c>
       <c r="V10" t="n">
-        <v>-5.0905</v>
+        <v>-2.7063</v>
       </c>
       <c r="W10" t="n">
-        <v>19.7323</v>
+        <v>-0.6982</v>
       </c>
       <c r="X10" t="n">
-        <v>-24.8233</v>
+        <v>-2.0081</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. SALOMON</t>
+          <t>J. PALAMOS MOLINS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.6699</v>
+        <v>-7.762000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.424799999999999</v>
+        <v>-18.734</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.2447</v>
+        <v>10.9723</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6248</v>
+        <v>9.943599999999998</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.9658</v>
+        <v>-4.4182</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3412000000000002</v>
+        <v>14.3616</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0667</v>
+        <v>24.6842</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2926</v>
+        <v>6.8248</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7738999999999998</v>
+        <v>17.859</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.6916</v>
+        <v>-14.7411</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.2585</v>
+        <v>-11.2432</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4329999999999999</v>
+        <v>-3.4978</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0534</v>
+        <v>-16.6327</v>
       </c>
       <c r="Q11" t="n">
-        <v>-10.6778</v>
+        <v>-51.9514</v>
       </c>
       <c r="R11" t="n">
-        <v>8.6244</v>
+        <v>35.3188</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.1582</v>
+        <v>0.1493000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1319</v>
+        <v>0.5009</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.0266</v>
+        <v>-0.3514999999999998</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.833</v>
+        <v>-1.2215</v>
       </c>
       <c r="W11" t="n">
-        <v>3.3181</v>
+        <v>8.032500000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.1513</v>
+        <v>-9.254100000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. RIVAS PALMER</t>
+          <t>H. SALOMON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.6026</v>
+        <v>-9.120100000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-19.1444</v>
+        <v>-5.3904</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5416</v>
+        <v>-3.7298</v>
       </c>
       <c r="G12" t="n">
-        <v>-18.086</v>
+        <v>-2.6248</v>
       </c>
       <c r="H12" t="n">
-        <v>-19.1309</v>
+        <v>-2.9658</v>
       </c>
       <c r="I12" t="n">
-        <v>1.044899999999999</v>
+        <v>0.3412000000000002</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.04210000000000047</v>
+        <v>2.0667</v>
       </c>
       <c r="K12" t="n">
-        <v>-8.898800000000001</v>
+        <v>1.2926</v>
       </c>
       <c r="L12" t="n">
-        <v>8.8568</v>
+        <v>0.7738999999999998</v>
       </c>
       <c r="M12" t="n">
-        <v>-18.0439</v>
+        <v>-4.6916</v>
       </c>
       <c r="N12" t="n">
-        <v>-10.2319</v>
+        <v>-4.2585</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.8121</v>
+        <v>-0.4329999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.000100000000000211</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q12" t="n">
-        <v>-26.489</v>
+        <v>-10.6778</v>
       </c>
       <c r="R12" t="n">
-        <v>26.4893</v>
+        <v>8.6244</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.3559</v>
+        <v>-1.6086</v>
       </c>
       <c r="T12" t="n">
-        <v>-7.5</v>
+        <v>-0.09750000000000009</v>
       </c>
       <c r="U12" t="n">
-        <v>2.144</v>
+        <v>-1.5112</v>
       </c>
       <c r="V12" t="n">
-        <v>7.839</v>
+        <v>-2.833</v>
       </c>
       <c r="W12" t="n">
-        <v>14.8866</v>
+        <v>3.3181</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.047700000000001</v>
+        <v>-6.1513</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. PALAMOS MOLINS</t>
+          <t>A. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.2154</v>
+        <v>-10.0587</v>
       </c>
       <c r="E13" t="n">
-        <v>-24.5883</v>
+        <v>-13.3173</v>
       </c>
       <c r="F13" t="n">
-        <v>6.372999999999999</v>
+        <v>3.2589</v>
       </c>
       <c r="G13" t="n">
-        <v>9.943599999999998</v>
+        <v>-18.086</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.4182</v>
+        <v>-19.1309</v>
       </c>
       <c r="I13" t="n">
-        <v>14.3616</v>
+        <v>1.044899999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>24.6842</v>
+        <v>-0.04210000000000047</v>
       </c>
       <c r="K13" t="n">
-        <v>6.8248</v>
+        <v>-8.898800000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>17.859</v>
+        <v>8.8568</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.7411</v>
+        <v>-18.0439</v>
       </c>
       <c r="N13" t="n">
-        <v>-11.2432</v>
+        <v>-10.2319</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.4978</v>
+        <v>-7.8121</v>
       </c>
       <c r="P13" t="n">
-        <v>-16.6327</v>
+        <v>-0.000100000000000211</v>
       </c>
       <c r="Q13" t="n">
-        <v>-51.9514</v>
+        <v>-26.489</v>
       </c>
       <c r="R13" t="n">
-        <v>35.3188</v>
+        <v>26.4893</v>
       </c>
       <c r="S13" t="n">
-        <v>-10.3043</v>
+        <v>0.1883999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.3533</v>
+        <v>-1.6732</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.9509</v>
+        <v>1.8613</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2215</v>
+        <v>7.839</v>
       </c>
       <c r="W13" t="n">
-        <v>8.032500000000001</v>
+        <v>14.8866</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.254100000000001</v>
+        <v>-7.047700000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>-39.5184</v>
+        <v>-30.9127</v>
       </c>
       <c r="E14" t="n">
-        <v>-34.1423</v>
+        <v>-28.4046</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.375999999999999</v>
+        <v>-2.5083</v>
       </c>
       <c r="G14" t="n">
         <v>-19.8268</v>
@@ -1546,13 +1546,13 @@
         <v>33.4707</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.6272</v>
+        <v>1.979</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.954499999999999</v>
+        <v>-0.2164000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6727999999999997</v>
+        <v>2.1953</v>
       </c>
       <c r="V14" t="n">
         <v>-2.5923</v>
@@ -1579,16 +1579,16 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>38.60019999999999</v>
+        <v>71.26190000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>14.45339999999998</v>
+        <v>28.28650000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>24.1483</v>
+        <v>42.977</v>
       </c>
       <c r="G15" t="n">
-        <v>77.7313</v>
+        <v>77.73130000000002</v>
       </c>
       <c r="H15" t="n">
         <v>-78.2748</v>
@@ -1597,10 +1597,10 @@
         <v>156.006</v>
       </c>
       <c r="J15" t="n">
-        <v>265.0369999999999</v>
+        <v>265.037</v>
       </c>
       <c r="K15" t="n">
-        <v>83.0779</v>
+        <v>83.07789999999999</v>
       </c>
       <c r="L15" t="n">
         <v>181.959</v>
@@ -1612,25 +1612,25 @@
         <v>-161.3544</v>
       </c>
       <c r="O15" t="n">
-        <v>-25.95389999999999</v>
+        <v>-25.9539</v>
       </c>
       <c r="P15" t="n">
         <v>-61.60270000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-420.9501999999999</v>
+        <v>-420.9502</v>
       </c>
       <c r="R15" t="n">
         <v>359.3489</v>
       </c>
       <c r="S15" t="n">
-        <v>16.60299999999999</v>
+        <v>49.2641</v>
       </c>
       <c r="T15" t="n">
-        <v>15.4587</v>
+        <v>29.2924</v>
       </c>
       <c r="U15" t="n">
-        <v>1.143200000000001</v>
+        <v>19.9715</v>
       </c>
       <c r="V15" t="n">
         <v>5.871200000000007</v>
